--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486312_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486312_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2548</v>
+        <v>2.7414</v>
       </c>
       <c r="E2" t="n">
-        <v>1.7721</v>
+        <v>1.5053</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4827</v>
+        <v>1.2361</v>
       </c>
       <c r="G2" t="n">
         <v>0.2992</v>
@@ -610,13 +610,13 @@
         <v>0.87</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9556</v>
+        <v>0.4422</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4026</v>
+        <v>0.1358</v>
       </c>
       <c r="U2" t="n">
-        <v>0.553</v>
+        <v>0.3064</v>
       </c>
       <c r="V2" t="n">
         <v>1.13</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2194</v>
+        <v>2.2888</v>
       </c>
       <c r="E3" t="n">
-        <v>1.749</v>
+        <v>1.9725</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4705</v>
+        <v>0.3163</v>
       </c>
       <c r="G3" t="n">
         <v>0.5571</v>
@@ -688,13 +688,13 @@
         <v>1.305</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2157</v>
+        <v>0.2851</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4831</v>
+        <v>0.7066</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2674</v>
+        <v>-0.4215</v>
       </c>
       <c r="V3" t="n">
         <v>1.6642</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. DIKE EGUN</t>
+          <t>A. URDIAIN LABAYEN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7798</v>
+        <v>1.8479</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5727</v>
+        <v>1.7449</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.7929</v>
+        <v>0.103</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0737</v>
+        <v>0.2407</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1191</v>
+        <v>-0.3347</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9546</v>
+        <v>0.5754</v>
       </c>
       <c r="J4" t="n">
-        <v>4.0414</v>
+        <v>0.7644</v>
       </c>
       <c r="K4" t="n">
-        <v>2.6644</v>
+        <v>0.1492</v>
       </c>
       <c r="L4" t="n">
-        <v>1.377</v>
+        <v>0.6152</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.9677</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.5453</v>
+        <v>-0.4838</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4224</v>
+        <v>-0.0399</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.435</v>
+        <v>0.6525</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.7401</v>
+        <v>-0.2175</v>
       </c>
       <c r="R4" t="n">
-        <v>1.305</v>
+        <v>0.87</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4764</v>
+        <v>-0.9355</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4252</v>
+        <v>-0.6922</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0512</v>
+        <v>-0.2434</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.3353</v>
+        <v>1.8902</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.1538</v>
+        <v>1.8902</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.1814</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. CAMACHO DE SÁ</t>
+          <t>G. DIKE EGUN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5984</v>
+        <v>0.8742</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2097</v>
+        <v>2.7904</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6112</v>
+        <v>-1.9162</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.197</v>
+        <v>2.0737</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3436</v>
+        <v>1.1191</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8534</v>
+        <v>0.9546</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2057</v>
+        <v>4.0414</v>
       </c>
       <c r="K5" t="n">
-        <v>1.4663</v>
+        <v>2.6644</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.2606</v>
+        <v>1.377</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4027</v>
+        <v>-1.9677</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.8098</v>
+        <v>-1.5453</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4072</v>
+        <v>-0.4224</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2175</v>
+        <v>-0.435</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.7401</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9576</v>
+        <v>1.305</v>
       </c>
       <c r="S5" t="n">
-        <v>3.1737</v>
+        <v>0.5708</v>
       </c>
       <c r="T5" t="n">
-        <v>2.9838</v>
+        <v>0.6429</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1899</v>
+        <v>-0.0721</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5958</v>
+        <v>-1.3353</v>
       </c>
       <c r="W5" t="n">
-        <v>0.7602</v>
+        <v>-0.1538</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.356</v>
+        <v>-1.1814</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. URDIAIN LABAYEN</t>
+          <t>D. AGBELESE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1359</v>
+        <v>0.5081</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3411</v>
+        <v>-0.1462</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2053</v>
+        <v>0.6542</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2407</v>
+        <v>1.6526</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3347</v>
+        <v>1.0462</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5754</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7644</v>
+        <v>0.8479</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1492</v>
+        <v>0.7331</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6152</v>
+        <v>0.1147</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5237000000000001</v>
+        <v>0.8047</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4838</v>
+        <v>0.3131</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0399</v>
+        <v>0.4916</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6525</v>
+        <v>-0.87</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2175</v>
+        <v>-2.1751</v>
       </c>
       <c r="R6" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.6475</v>
+        <v>-0.0793</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0959</v>
+        <v>-0.1442</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5516</v>
+        <v>0.0649</v>
       </c>
       <c r="V6" t="n">
-        <v>1.8902</v>
+        <v>-0.1952</v>
       </c>
       <c r="W6" t="n">
-        <v>1.8902</v>
+        <v>1.3252</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.5204</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. AGBELESE</t>
+          <t>H. ATENCIA SUAREZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4742</v>
+        <v>0.4849</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.55</v>
+        <v>-0.0212</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0241</v>
+        <v>0.5061</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6526</v>
+        <v>-0.9558</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0462</v>
+        <v>0.4897</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6064000000000001</v>
+        <v>-1.4455</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8479</v>
+        <v>-0.1467</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7331</v>
+        <v>2.0685</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1147</v>
+        <v>-2.2152</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8047</v>
+        <v>-0.8091</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3131</v>
+        <v>-1.5788</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4916</v>
+        <v>0.7697000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.1751</v>
+        <v>-1.7401</v>
       </c>
       <c r="R7" t="n">
-        <v>1.305</v>
+        <v>2.3926</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1132</v>
+        <v>-0.6808</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.548</v>
+        <v>0.1707</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4348</v>
+        <v>-0.8514</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1952</v>
+        <v>1.469</v>
       </c>
       <c r="W7" t="n">
-        <v>1.3252</v>
+        <v>1.695</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.5204</v>
+        <v>-0.226</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1638</v>
+        <v>0.1012</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6106</v>
+        <v>-0.7655999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7743</v>
+        <v>0.8668</v>
       </c>
       <c r="G8" t="n">
         <v>1.3951</v>
@@ -1078,13 +1078,13 @@
         <v>1.0875</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1438</v>
+        <v>-0.2064</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0601</v>
+        <v>-0.0949</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2039</v>
+        <v>-0.1115</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8972</v>
+        <v>-0.1852</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8044</v>
+        <v>-1.4006</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9072</v>
+        <v>1.2154</v>
       </c>
       <c r="G9" t="n">
         <v>0.6253</v>
@@ -1156,13 +1156,13 @@
         <v>0.6525</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.87</v>
+        <v>-0.158</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.2812</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1851</v>
+        <v>0.1232</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>H. ATENCIA SUAREZ</t>
+          <t>N. CAMACHO DE SÁ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0642</v>
+        <v>-0.4979</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1387</v>
+        <v>0.4215</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0746</v>
+        <v>-0.9195</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9558</v>
+        <v>-1.197</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4897</v>
+        <v>-0.3436</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.4455</v>
+        <v>-0.8534</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1467</v>
+        <v>0.2057</v>
       </c>
       <c r="K10" t="n">
-        <v>2.0685</v>
+        <v>1.4663</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.2152</v>
+        <v>-1.2606</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8091</v>
+        <v>-1.4027</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.5788</v>
+        <v>-1.8098</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7697000000000001</v>
+        <v>0.4072</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6525</v>
+        <v>0.2175</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.7401</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3926</v>
+        <v>1.9576</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.2299</v>
+        <v>1.0773</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9469</v>
+        <v>1.1957</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.2829</v>
+        <v>-0.1184</v>
       </c>
       <c r="V10" t="n">
-        <v>1.469</v>
+        <v>-0.5958</v>
       </c>
       <c r="W10" t="n">
-        <v>1.695</v>
+        <v>0.7602</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.226</v>
+        <v>-1.356</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.576</v>
+        <v>-2.26</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3011</v>
+        <v>-1.0776</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2749</v>
+        <v>-1.1825</v>
       </c>
       <c r="G11" t="n">
         <v>0.1175</v>
@@ -1312,13 +1312,13 @@
         <v>0.6525</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7158</v>
+        <v>-0.3999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.548</v>
+        <v>-0.3245</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1679</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>-1.3252</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9252</v>
+        <v>-2.3972</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0454</v>
+        <v>0.6042</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.9706</v>
+        <v>-3.0014</v>
       </c>
       <c r="G12" t="n">
         <v>-0.2507</v>
@@ -1390,13 +1390,13 @@
         <v>0.6525</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1011</v>
+        <v>0.4269</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.125</v>
+        <v>0.4338</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0239</v>
+        <v>-0.0069</v>
       </c>
       <c r="V12" t="n">
         <v>-1.921</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.163699999999999</v>
+        <v>3.506200000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>5.285200000000001</v>
+        <v>5.6276</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.121499999999999</v>
+        <v>-2.1217</v>
       </c>
       <c r="G13" t="n">
         <v>4.5577</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4101000000000006</v>
+        <v>0.4101000000000001</v>
       </c>
       <c r="I13" t="n">
         <v>4.1477</v>
@@ -1444,10 +1444,10 @@
         <v>10.3726</v>
       </c>
       <c r="K13" t="n">
-        <v>6.571300000000001</v>
+        <v>6.571299999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>3.8011</v>
+        <v>3.801100000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-5.8148</v>
@@ -1456,7 +1456,7 @@
         <v>-6.161</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3463999999999999</v>
+        <v>0.3464000000000002</v>
       </c>
       <c r="P13" t="n">
         <v>-2.175</v>
@@ -1468,22 +1468,22 @@
         <v>13.0502</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0001000000000006274</v>
+        <v>0.3423999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>1.406</v>
+        <v>1.7485</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.406</v>
+        <v>-1.4061</v>
       </c>
       <c r="V13" t="n">
-        <v>0.780900000000001</v>
+        <v>0.7809000000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>8.732199999999999</v>
+        <v>8.732200000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.951199999999999</v>
+        <v>-7.9512</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.3187</v>
+        <v>4.1903</v>
       </c>
       <c r="E14" t="n">
         <v>3.9856</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3331</v>
+        <v>0.2047</v>
       </c>
       <c r="G14" t="n">
         <v>1.0514</v>
@@ -1546,13 +1546,13 @@
         <v>2.6101</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0276</v>
+        <v>0.8992</v>
       </c>
       <c r="T14" t="n">
         <v>0.6237</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4039</v>
+        <v>0.2755</v>
       </c>
       <c r="V14" t="n">
         <v>0.9347</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8281</v>
+        <v>2.674</v>
       </c>
       <c r="E15" t="n">
         <v>3.4269</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5987</v>
+        <v>-0.7529</v>
       </c>
       <c r="G15" t="n">
         <v>1.0969</v>
@@ -1624,13 +1624,13 @@
         <v>1.5225</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1388</v>
+        <v>-0.2929</v>
       </c>
       <c r="T15" t="n">
         <v>-0.2824</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1436</v>
+        <v>-0.0105</v>
       </c>
       <c r="V15" t="n">
         <v>0.5649999999999999</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7808</v>
+        <v>0.7256</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0168</v>
+        <v>-0.095</v>
       </c>
       <c r="F16" t="n">
-        <v>0.764</v>
+        <v>0.8205</v>
       </c>
       <c r="G16" t="n">
         <v>0.0529</v>
@@ -1702,13 +1702,13 @@
         <v>1.7401</v>
       </c>
       <c r="S16" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.0201</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4951</v>
+        <v>0.3833</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4198</v>
+        <v>-0.3632</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>P. MOLINS CALDERON</t>
+          <t>T. MCFADDEN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.005</v>
+        <v>-0.0236</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1059</v>
+        <v>1.5491</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1008</v>
+        <v>-1.5728</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4762</v>
+        <v>-1.4347</v>
       </c>
       <c r="H17" t="n">
-        <v>0.14</v>
+        <v>0.1063</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3363</v>
+        <v>-1.5411</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4612</v>
+        <v>0.6038</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4229</v>
+        <v>1.1711</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0382</v>
+        <v>-0.5673</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0151</v>
+        <v>-2.0386</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2829</v>
+        <v>-1.0648</v>
       </c>
       <c r="O17" t="n">
-        <v>0.298</v>
+        <v>-0.9738</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.435</v>
+        <v>0.435</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0875</v>
+        <v>-1.305</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6525</v>
+        <v>1.7401</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0463</v>
+        <v>-0.5236</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4795</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4332</v>
+        <v>-0.514</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.4997</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.2599</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. MCFADDEN</t>
+          <t>P. MOLINS CALDERON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0274</v>
+        <v>-0.0474</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8844</v>
+        <v>-0.9941</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.9118</v>
+        <v>0.9467</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.4347</v>
+        <v>0.4762</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1063</v>
+        <v>0.14</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.5411</v>
+        <v>0.3363</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6038</v>
+        <v>0.4612</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1711</v>
+        <v>0.4229</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5673</v>
+        <v>0.0382</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.0386</v>
+        <v>0.0151</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0648</v>
+        <v>-0.2829</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9738</v>
+        <v>0.298</v>
       </c>
       <c r="P18" t="n">
-        <v>0.435</v>
+        <v>-0.435</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.305</v>
+        <v>-1.0875</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7401</v>
+        <v>0.6525</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5274</v>
+        <v>-0.0886</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3257</v>
+        <v>-0.3677</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8531</v>
+        <v>0.2791</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4997</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.2599</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.7602</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.14</v>
+        <v>-0.0604</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3098</v>
+        <v>1.0863</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4498</v>
+        <v>-1.1467</v>
       </c>
       <c r="G19" t="n">
         <v>-0.2331</v>
@@ -1936,13 +1936,13 @@
         <v>1.0875</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5053</v>
+        <v>0.5849</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7006</v>
+        <v>0.4771</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1953</v>
+        <v>0.1078</v>
       </c>
       <c r="V19" t="n">
         <v>-1.4997</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. CONE</t>
+          <t>N. GALETTE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8566</v>
+        <v>-1.0642</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9117</v>
+        <v>-0.882</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0551</v>
+        <v>-0.1821</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.8856</v>
+        <v>-0.9785</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.8766</v>
+        <v>-0.9785</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2455</v>
+        <v>-0.7451</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9553</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2008</v>
+        <v>-0.7451</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.6401</v>
+        <v>-0.2335</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9643</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6758</v>
+        <v>-0.2335</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.3926</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1751</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.072</v>
+        <v>-0.0856</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9661999999999999</v>
+        <v>-0.137</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1059</v>
+        <v>0.0514</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1745</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7602</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5857</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>N. GALETTE</t>
+          <t>J. CONE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.095</v>
+        <v>-1.0967</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.882</v>
+        <v>-1.0235</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2129</v>
+        <v>-0.0733</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9785</v>
+        <v>-1.8856</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9785</v>
+        <v>-1.8766</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7451</v>
+        <v>-0.2455</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>0.9553</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7451</v>
+        <v>-1.2008</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2335</v>
+        <v>-1.6401</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>-0.9643</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2335</v>
+        <v>-0.6758</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.3926</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.1751</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1164</v>
+        <v>0.8319</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.137</v>
+        <v>0.8544</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0205</v>
+        <v>-0.0225</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.1745</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.7602</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.5857</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0156</v>
+        <v>-3.0304</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.4432</v>
+        <v>-2.8844</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5724</v>
+        <v>-0.146</v>
       </c>
       <c r="G22" t="n">
         <v>0.6917</v>
@@ -2170,13 +2170,13 @@
         <v>3.0451</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7295</v>
+        <v>0.2557</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2584</v>
+        <v>0.3004</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4712</v>
+        <v>-0.0448</v>
       </c>
       <c r="V22" t="n">
         <v>-2.4552</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.9518</v>
+        <v>-4.6859</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.4197</v>
+        <v>-1.308</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.532</v>
+        <v>-3.3779</v>
       </c>
       <c r="G23" t="n">
         <v>-3.395</v>
@@ -2248,13 +2248,13 @@
         <v>0.6525</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1218</v>
+        <v>-0.8559</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.548</v>
+        <v>-0.4362</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5738</v>
+        <v>-0.4197</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,31 +2281,31 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.163800000000001</v>
+        <v>-2.4187</v>
       </c>
       <c r="E24" t="n">
-        <v>2.861000000000001</v>
+        <v>2.860900000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-6.0246</v>
+        <v>-5.2798</v>
       </c>
       <c r="G24" t="n">
         <v>-4.5578</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.4101000000000004</v>
+        <v>-0.4100999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-4.1476</v>
+        <v>-4.147600000000001</v>
       </c>
       <c r="J24" t="n">
         <v>5.8146</v>
       </c>
       <c r="K24" t="n">
-        <v>6.161</v>
+        <v>6.161000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.3465</v>
+        <v>-0.3464999999999998</v>
       </c>
       <c r="M24" t="n">
         <v>-10.3725</v>
@@ -2326,16 +2326,16 @@
         <v>15.2255</v>
       </c>
       <c r="S24" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0.7452000000000002</v>
       </c>
       <c r="T24" t="n">
         <v>1.406</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.4061</v>
+        <v>-0.6609</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.7810000000000001</v>
+        <v>-0.7810000000000006</v>
       </c>
       <c r="W24" t="n">
         <v>8.6906</v>
